--- a/AAAGameData/DataTables/Item/ItemWithEffectTable_Tool.xlsx
+++ b/AAAGameData/DataTables/Item/ItemWithEffectTable_Tool.xlsx
@@ -62,10 +62,10 @@
     <t>SpriteName</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescriptionKey</t>
   </si>
   <si>
     <t>Tags</t>
